--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.01166</v>
+        <v>17.04755</v>
       </c>
       <c r="D2" t="n">
-        <v>16.77552</v>
+        <v>16.8954</v>
       </c>
       <c r="E2" t="n">
-        <v>17.11808</v>
+        <v>16.94851</v>
       </c>
       <c r="F2" t="n">
-        <v>42.45038</v>
+        <v>43.53573</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05096</v>
+        <v>0.05072</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80018</v>
+        <v>1.87662</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.02996</v>
+        <v>17.05345</v>
       </c>
       <c r="D3" t="n">
-        <v>16.81159</v>
+        <v>17.02431</v>
       </c>
       <c r="E3" t="n">
-        <v>16.98672</v>
+        <v>17.03241</v>
       </c>
       <c r="F3" t="n">
-        <v>43.26469</v>
+        <v>42.62783</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0512</v>
+        <v>0.05114</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83592</v>
+        <v>1.84648</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.1424</v>
+        <v>17.17352</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66972</v>
+        <v>16.76587</v>
       </c>
       <c r="E4" t="n">
-        <v>16.94032</v>
+        <v>16.96269</v>
       </c>
       <c r="F4" t="n">
-        <v>43.1144</v>
+        <v>43.6297</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05123</v>
+        <v>0.05108</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83577</v>
+        <v>1.85674</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.62905</v>
+        <v>16.85307</v>
       </c>
       <c r="D6" t="n">
-        <v>16.37255</v>
+        <v>15.83674</v>
       </c>
       <c r="E6" t="n">
-        <v>16.59724</v>
+        <v>16.42737</v>
       </c>
       <c r="F6" t="n">
-        <v>21.7046</v>
+        <v>21.7955</v>
       </c>
       <c r="G6" t="n">
-        <v>34.35339</v>
+        <v>34.38873</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.04934</v>
+        <v>16.88954</v>
       </c>
       <c r="D7" t="n">
-        <v>15.96741</v>
+        <v>16.01524</v>
       </c>
       <c r="E7" t="n">
-        <v>16.649</v>
+        <v>16.77781</v>
       </c>
       <c r="F7" t="n">
-        <v>21.97934</v>
+        <v>21.931</v>
       </c>
       <c r="G7" t="n">
-        <v>34.73939</v>
+        <v>34.75136</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.73102</v>
+        <v>16.91583</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12753</v>
+        <v>16.43748</v>
       </c>
       <c r="E8" t="n">
-        <v>16.39779</v>
+        <v>16.80364</v>
       </c>
       <c r="F8" t="n">
-        <v>22.09956</v>
+        <v>22.45483</v>
       </c>
       <c r="G8" t="n">
-        <v>34.74099</v>
+        <v>34.57814</v>
       </c>
     </row>
   </sheetData>
